--- a/Result/profitability/3689.xlsx
+++ b/Result/profitability/3689.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM66"/>
+  <dimension ref="A1:AM67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>3.44</v>
       </c>
       <c r="M2" t="n">
-        <v>2.19125</v>
+        <v>2.2025</v>
       </c>
       <c r="N2" t="n">
-        <v>29.08375</v>
+        <v>28.93875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-1.67</v>
       </c>
       <c r="M3" t="n">
-        <v>1.69</v>
+        <v>1.73375</v>
       </c>
       <c r="N3" t="n">
-        <v>29.425</v>
+        <v>29.145</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>3.16</v>
       </c>
       <c r="M4" t="n">
-        <v>1.825</v>
+        <v>1.85</v>
       </c>
       <c r="N4" t="n">
-        <v>28.63625</v>
+        <v>28.56875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>3.3</v>
       </c>
       <c r="M5" t="n">
-        <v>1.95875</v>
+        <v>2.05625</v>
       </c>
       <c r="N5" t="n">
-        <v>28.4175</v>
+        <v>28.4125</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -8812,6 +8812,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>3689</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>2221</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1576</v>
+      </c>
+      <c r="E67" t="n">
+        <v>645</v>
+      </c>
+      <c r="F67" t="n">
+        <v>29.02</v>
+      </c>
+      <c r="G67" t="n">
+        <v>290</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>13.05%</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>6</v>
+      </c>
+      <c r="J67" t="n">
+        <v>296</v>
+      </c>
+      <c r="K67" t="n">
+        <v>217</v>
+      </c>
+      <c r="L67" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="M67" t="n">
+        <v>2.065</v>
+      </c>
+      <c r="N67" t="n">
+        <v>30.0425</v>
+      </c>
+      <c r="O67" t="n">
+        <v>1</v>
+      </c>
+      <c r="P67" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>1</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="n">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
+      </c>
+      <c r="V67" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W67" t="n">
+        <v>0.3900000000000001</v>
+      </c>
+      <c r="X67" t="n">
+        <v>0.1911764705882353</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>-1.23</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>-0.04066115702479345</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>0.7800000000000002</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>0.4727272727272729</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>-0.03999999999999915</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>-0.001376462491397112</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK67" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL67" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM67" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
